--- a/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:01:00+00:00</t>
+    <t>2026-06-19T13:53:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
+++ b/main/ig/StructureDefinition-as-ext-person-statut-etat-civil.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
